--- a/artfynd/A 2643-2025 artfynd.xlsx
+++ b/artfynd/A 2643-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121568922</v>
+        <v>121568916</v>
       </c>
       <c r="B2" t="n">
-        <v>78365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759838</v>
+        <v>759938</v>
       </c>
       <c r="R2" t="n">
-        <v>7116552</v>
+        <v>7116501</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121568918</v>
+        <v>121568919</v>
       </c>
       <c r="B3" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759816</v>
+        <v>759823</v>
       </c>
       <c r="R3" t="n">
-        <v>7116271</v>
+        <v>7116289</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121568916</v>
+        <v>121568917</v>
       </c>
       <c r="B4" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759938</v>
+        <v>759926</v>
       </c>
       <c r="R4" t="n">
-        <v>7116501</v>
+        <v>7116457</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121568917</v>
+        <v>121568918</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759926</v>
+        <v>759816</v>
       </c>
       <c r="R5" t="n">
-        <v>7116457</v>
+        <v>7116271</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121568921</v>
+        <v>121568920</v>
       </c>
       <c r="B6" t="n">
-        <v>78365</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759807</v>
+        <v>759822</v>
       </c>
       <c r="R6" t="n">
-        <v>7116470</v>
+        <v>7116319</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121568920</v>
+        <v>121568921</v>
       </c>
       <c r="B7" t="n">
-        <v>78365</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759822</v>
+        <v>759807</v>
       </c>
       <c r="R7" t="n">
-        <v>7116319</v>
+        <v>7116470</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121568919</v>
+        <v>121568922</v>
       </c>
       <c r="B8" t="n">
-        <v>92018</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759823</v>
+        <v>759838</v>
       </c>
       <c r="R8" t="n">
-        <v>7116289</v>
+        <v>7116552</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 2643-2025 artfynd.xlsx
+++ b/artfynd/A 2643-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568916</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568919</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568917</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568918</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568920</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568921</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568922</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>